--- a/astro-site/public/dl/kit-gestion-personal/07-directorio-plantilla.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/07-directorio-plantilla.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Plantilla" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Vencimientos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vencimientos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Plantilla'!$A$4:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plantilla'!$A$4:$O$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Vencimientos'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,8 +22,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
-    <numFmt formatCode="€#,##0.00" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="€#,##0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -138,49 +139,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -540,15 +541,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -556,6 +558,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -584,9 +587,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -615,9 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -646,8 +645,25 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -656,26 +672,26 @@
   <sheetPr>
     <tabColor rgb="0000695C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="24"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="18"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="22"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
-    <col customWidth="1" max="13" min="13" width="18"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
-    <col customWidth="1" max="15" min="15" width="10"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -692,6 +708,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1279,6 +1296,7 @@
       <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
@@ -1294,14 +1312,23 @@
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34" type="list">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Indefinido,Temporal,Prácticas,Formación,Fijo-discontinuo"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Completa,Parcial"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1310,16 +1337,16 @@
   <sheetPr>
     <tabColor rgb="00004D40"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="24"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1344,9 +1371,10 @@
       </c>
       <c r="B3" s="13">
         <f>TODAY()</f>
-        <v/>
-      </c>
-    </row>
+        <v>46256.0</v>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -1711,6 +1739,8 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -1875,6 +1905,8 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -1888,6 +1920,15 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/07-directorio-plantilla.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/07-directorio-plantilla.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vencimientos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plantilla" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Vencimientos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plantilla'!$A$4:$O$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Vencimientos'!$6:$6</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'Plantilla'!$A$4:$O$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="€#,##0.00"/>
+    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt formatCode="€#,##0.00" numFmtId="165"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -139,49 +138,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -541,16 +540,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -558,7 +556,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -587,7 +584,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -616,7 +615,9 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="B13" t="inlineStr"/>
+    </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -645,25 +646,8 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -672,26 +656,26 @@
   <sheetPr>
     <tabColor rgb="0000695C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col customWidth="1" max="1" min="1" width="24"/>
+    <col customWidth="1" max="2" min="2" width="16"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
+    <col customWidth="1" max="4" min="4" width="16"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
+    <col customWidth="1" max="7" min="7" width="14"/>
+    <col customWidth="1" max="8" min="8" width="14"/>
+    <col customWidth="1" max="9" min="9" width="18"/>
+    <col customWidth="1" max="10" min="10" width="14"/>
+    <col customWidth="1" max="11" min="11" width="22"/>
+    <col customWidth="1" max="12" min="12" width="20"/>
+    <col customWidth="1" max="13" min="13" width="18"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
+    <col customWidth="1" max="15" min="15" width="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,7 +692,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1296,7 +1279,6 @@
       <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
@@ -1312,23 +1294,14 @@
     <mergeCell ref="A2:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34" type="list">
       <formula1>"Indefinido,Temporal,Prácticas,Formación,Fijo-discontinuo"</formula1>
     </dataValidation>
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" type="list">
       <formula1>"Completa,Parcial"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1337,16 +1310,16 @@
   <sheetPr>
     <tabColor rgb="00004D40"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col customWidth="1" max="1" min="1" width="24"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
+    <col customWidth="1" max="4" min="4" width="18"/>
+    <col customWidth="1" max="5" min="5" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1371,10 +1344,9 @@
       </c>
       <c r="B3" s="13">
         <f>TODAY()</f>
-        <v>46256.0</v>
-      </c>
-    </row>
-    <row r="4"/>
+        <v/>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -1739,8 +1711,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -1905,8 +1875,6 @@
         <v/>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -1920,15 +1888,6 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>